--- a/kobo/appeals_monitor_feedback.xlsx
+++ b/kobo/appeals_monitor_feedback.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodekruis-my.sharepoint.com/personal/jmargutti_redcross_nl/Documents/Rode Kruis/510/appeals-monitor/kobo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_96B1FF8C77A348DFF8FA0826381CBB28B6AD0C6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A39A0F3-D8BF-41D5-A5E1-004B0FAA4996}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_96B1FF8C77A348DFF8FA0826381CBB28B6AD0C6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6524AF87-AB4F-402F-90E9-638B5D474D7D}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -694,13 +694,13 @@
     <t>English (en)</t>
   </si>
   <si>
+    <t>Comparing budgets, targets or activities against other operations</t>
+  </si>
+  <si>
     <t>**Appeals Monitor - your feedback**
-The Appeals Monitor emails you a short summary every time a new IFRC appeal document (a DREF operation, emergency appeal, operational strategy or anticipatory-action activation) is published in one of the sectors you follow.
+The Appeals Monitor emails you a short summary every time a new IFRC appeal document (a DREF operation, emergency appeal, operational strategy or anticipatory-action activation) is published and matches one of the sectors you follow.
 We would like to know whether it is actually useful to you, and what we should build next. This takes about 5 minutes. All questions are optional unless marked.
 Your answers will only be used to improve the service.</t>
-  </si>
-  <si>
-    <t>Comparing budgets, targets or activities against other operations</t>
   </si>
 </sst>
 </file>
@@ -762,6 +762,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1110,7 +1114,7 @@
         <v>130</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -1892,7 +1896,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">

--- a/kobo/appeals_monitor_feedback.xlsx
+++ b/kobo/appeals_monitor_feedback.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodekruis-my.sharepoint.com/personal/jmargutti_redcross_nl/Documents/Rode Kruis/510/appeals-monitor/kobo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JMargutti\OneDrive - Rode Kruis\Rode Kruis\510\appeals-monitor\kobo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_96B1FF8C77A348DFF8FA0826381CBB28B6AD0C6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6524AF87-AB4F-402F-90E9-638B5D474D7D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06651E35-F0C9-494A-B936-CC03EE2A41B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="208">
   <si>
     <t>list_name</t>
   </si>
@@ -141,12 +141,6 @@
     <t>benchmark</t>
   </si>
   <si>
-    <t>cva_specific</t>
-  </si>
-  <si>
-    <t>Tracking cash and voucher assistance set-ups (modality, FSP, digital tools)</t>
-  </si>
-  <si>
     <t>contact_ns</t>
   </si>
   <si>
@@ -255,9 +249,6 @@
     <t>filter_country</t>
   </si>
   <si>
-    <t>Filter by country or region, not only by sector</t>
-  </si>
-  <si>
     <t>filter_hazard</t>
   </si>
   <si>
@@ -339,48 +330,6 @@
     <t>Somewhere else</t>
   </si>
   <si>
-    <t>doctypes</t>
-  </si>
-  <si>
-    <t>current_ok</t>
-  </si>
-  <si>
-    <t>The documents currently covered are enough</t>
-  </si>
-  <si>
-    <t>ops_updates</t>
-  </si>
-  <si>
-    <t>Operation updates</t>
-  </si>
-  <si>
-    <t>final_reports</t>
-  </si>
-  <si>
-    <t>Final reports</t>
-  </si>
-  <si>
-    <t>eplan</t>
-  </si>
-  <si>
-    <t>Emergency plans of action (EPoA)</t>
-  </si>
-  <si>
-    <t>sitreps</t>
-  </si>
-  <si>
-    <t>Situation reports</t>
-  </si>
-  <si>
-    <t>lessons</t>
-  </si>
-  <si>
-    <t>Lessons learned and evaluations</t>
-  </si>
-  <si>
-    <t>Other documents</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -622,15 +571,6 @@
   </si>
   <si>
     <t>selected(${preferred_channels}, 'other')</t>
-  </si>
-  <si>
-    <t>select_multiple doctypes</t>
-  </si>
-  <si>
-    <t>extra_doctypes</t>
-  </si>
-  <si>
-    <t>Which other documents should the monitor cover? Select all that apply.</t>
   </si>
   <si>
     <t>doctypes_other</t>
@@ -701,6 +641,15 @@
 The Appeals Monitor emails you a short summary every time a new IFRC appeal document (a DREF operation, emergency appeal, operational strategy or anticipatory-action activation) is published and matches one of the sectors you follow.
 We would like to know whether it is actually useful to you, and what we should build next. This takes about 5 minutes. All questions are optional unless marked.
 Your answers will only be used to improve the service.</t>
+  </si>
+  <si>
+    <t>sector_specific</t>
+  </si>
+  <si>
+    <t>Tracking interventions in my sector (e.g. CVA modality, FSP, or digital tools)</t>
+  </si>
+  <si>
+    <t>Filter by country, not only by region and sector</t>
   </si>
 </sst>
 </file>
@@ -762,10 +711,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1053,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1068,7 +1013,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1077,48 +1022,48 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1127,40 +1072,40 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1169,20 +1114,20 @@
     </row>
     <row r="6" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1190,20 +1135,20 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1211,20 +1156,20 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -1232,20 +1177,20 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -1253,10 +1198,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1268,63 +1213,63 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -1333,44 +1278,44 @@
     </row>
     <row r="14" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1379,79 +1324,79 @@
     </row>
     <row r="16" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1463,84 +1408,84 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1549,20 +1494,20 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -1570,121 +1515,102 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="E26" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>208</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2" t="s">
-        <v>128</v>
-      </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="E29" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1896,7 +1822,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1904,10 +1830,10 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1915,10 +1841,10 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1929,7 +1855,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1937,407 +1863,365 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2357,36 +2241,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/kobo/appeals_monitor_feedback.xlsx
+++ b/kobo/appeals_monitor_feedback.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JMargutti\OneDrive - Rode Kruis\Rode Kruis\510\appeals-monitor\kobo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06651E35-F0C9-494A-B936-CC03EE2A41B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87417E9B-C586-4DCA-9053-6DFFA9C516BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="205">
   <si>
     <t>list_name</t>
   </si>
@@ -571,15 +571,6 @@
   </si>
   <si>
     <t>selected(${preferred_channels}, 'other')</t>
-  </si>
-  <si>
-    <t>doctypes_other</t>
-  </si>
-  <si>
-    <t>Please specify the other documents</t>
-  </si>
-  <si>
-    <t>selected(${extra_doctypes}, 'other')</t>
   </si>
   <si>
     <t>missing_content</t>
@@ -998,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1059,7 +1050,7 @@
         <v>113</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -1523,16 +1514,18 @@
       <c r="C25" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
@@ -1544,9 +1537,7 @@
       <c r="C26" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>188</v>
-      </c>
+      <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
         <v>111</v>
       </c>
@@ -1557,60 +1548,39 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>190</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2" t="s">
-        <v>152</v>
-      </c>
+      <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1822,7 +1792,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1830,10 +1800,10 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2020,7 +1990,7 @@
         <v>74</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2241,36 +2211,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
